--- a/output/Tables/7000 steps/Resampling/HIA_per_disease_7000steps.xlsx
+++ b/output/Tables/7000 steps/Resampling/HIA_per_disease_7000steps.xlsx
@@ -480,13 +480,13 @@
         <v>88204.90399999999</v>
       </c>
       <c r="E3">
-        <v>9551.522999999999</v>
+        <v>9552.76</v>
       </c>
       <c r="F3">
-        <v>5781.942</v>
+        <v>5782.386</v>
       </c>
       <c r="G3">
-        <v>13653.301</v>
+        <v>13659.068</v>
       </c>
       <c r="H3">
         <v>3440382243.517</v>
@@ -498,13 +498,13 @@
         <v>4918917378.5</v>
       </c>
       <c r="K3">
-        <v>1270900279.013</v>
+        <v>1271133647.421</v>
       </c>
       <c r="L3">
-        <v>771536297.096</v>
+        <v>771535429.337</v>
       </c>
       <c r="M3">
-        <v>1816464579.162</v>
+        <v>1817000302.117</v>
       </c>
     </row>
     <row r="4">
@@ -523,13 +523,13 @@
         <v>10150.134</v>
       </c>
       <c r="E4">
-        <v>1357.606</v>
+        <v>1357.315</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>2819.511</v>
+        <v>2817.999</v>
       </c>
       <c r="H4">
         <v>216189306.525</v>
@@ -541,13 +541,13 @@
         <v>448597467.593</v>
       </c>
       <c r="K4">
-        <v>180573924.763</v>
+        <v>180545129.916</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>374813638.429</v>
+        <v>374563020.504</v>
       </c>
     </row>
     <row r="5">
@@ -566,13 +566,13 @@
         <v>66662.76300000001</v>
       </c>
       <c r="E5">
-        <v>5482.33</v>
+        <v>5482.507</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>11390.577</v>
+        <v>11389.815</v>
       </c>
       <c r="H5">
         <v>475635616.627</v>
@@ -584,13 +584,13 @@
         <v>986842961.6900001</v>
       </c>
       <c r="K5">
-        <v>728321996.908</v>
+        <v>728409642.6339999</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>1511289448.944</v>
+        <v>1511755829.214</v>
       </c>
     </row>
     <row r="6">
@@ -609,13 +609,13 @@
         <v>81705.671</v>
       </c>
       <c r="E6">
-        <v>10535.704</v>
+        <v>10537.799</v>
       </c>
       <c r="F6">
-        <v>518.14</v>
+        <v>518.302</v>
       </c>
       <c r="G6">
-        <v>20037.693</v>
+        <v>20032.237</v>
       </c>
       <c r="H6">
         <v>3228039584.576</v>
@@ -627,13 +627,13 @@
         <v>6142389971.731</v>
       </c>
       <c r="K6">
-        <v>1400781205.739</v>
+        <v>1400988910.205</v>
       </c>
       <c r="L6">
-        <v>69491810.832</v>
+        <v>69500187.405</v>
       </c>
       <c r="M6">
-        <v>2669918750.262</v>
+        <v>2669323078.403</v>
       </c>
     </row>
     <row r="7">
@@ -652,13 +652,13 @@
         <v>27351.407</v>
       </c>
       <c r="E7">
-        <v>4276.183</v>
+        <v>4276.448</v>
       </c>
       <c r="F7">
-        <v>2913.245</v>
+        <v>2912.609</v>
       </c>
       <c r="G7">
-        <v>5816.284</v>
+        <v>5818.86</v>
       </c>
       <c r="H7">
         <v>336936413.71</v>
@@ -670,13 +670,13 @@
         <v>460611975.77</v>
       </c>
       <c r="K7">
-        <v>568588106.368</v>
+        <v>568599158.069</v>
       </c>
       <c r="L7">
-        <v>388085269.391</v>
+        <v>388001583.682</v>
       </c>
       <c r="M7">
-        <v>772905556.1109999</v>
+        <v>773103489.034</v>
       </c>
     </row>
     <row r="8">
@@ -695,13 +695,13 @@
         <v>1645028.046</v>
       </c>
       <c r="E8">
-        <v>1387460.765</v>
+        <v>1387587.021</v>
       </c>
       <c r="F8">
-        <v>946296.442</v>
+        <v>946219.238</v>
       </c>
       <c r="G8">
-        <v>1898577.708</v>
+        <v>1899449.451</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -713,13 +713,13 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>184586059556.5</v>
+        <v>184595742003.551</v>
       </c>
       <c r="L8">
-        <v>125928650932.124</v>
+        <v>125886456946.129</v>
       </c>
       <c r="M8">
-        <v>252365646105.899</v>
+        <v>252469363580.521</v>
       </c>
     </row>
     <row r="9">
@@ -738,13 +738,13 @@
         <v>1919102.925</v>
       </c>
       <c r="E9">
-        <v>1418664.111</v>
+        <v>1418793.85</v>
       </c>
       <c r="F9">
-        <v>955509.7690000001</v>
+        <v>955432.535</v>
       </c>
       <c r="G9">
-        <v>1952295.074</v>
+        <v>1953167.43</v>
       </c>
       <c r="H9">
         <v>7697183164.955001</v>
@@ -756,13 +756,13 @@
         <v>12957359755.284</v>
       </c>
       <c r="K9">
-        <v>188735225069.291</v>
+        <v>188745418491.796</v>
       </c>
       <c r="L9">
-        <v>127157764309.443</v>
+        <v>127115494146.553</v>
       </c>
       <c r="M9">
-        <v>259511038078.807</v>
+        <v>259615109299.793</v>
       </c>
     </row>
     <row r="10">
@@ -781,13 +781,13 @@
         <v>2142760.262</v>
       </c>
       <c r="E10">
-        <v>1700083.471</v>
+        <v>1700213.21</v>
       </c>
       <c r="F10">
-        <v>1161243.403</v>
+        <v>1161166.169</v>
       </c>
       <c r="G10">
-        <v>2316866.392</v>
+        <v>2317738.748</v>
       </c>
       <c r="H10">
         <v>7697183164.955001</v>
@@ -799,13 +799,13 @@
         <v>12957359755.284</v>
       </c>
       <c r="K10">
-        <v>226164842788.412</v>
+        <v>226175036210.917</v>
       </c>
       <c r="L10">
-        <v>154562972281.236</v>
+        <v>154520702118.346</v>
       </c>
       <c r="M10">
-        <v>308002290260.663</v>
+        <v>308106361481.649</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/7000 steps/Resampling/HIA_per_disease_7000steps.xlsx
+++ b/output/Tables/7000 steps/Resampling/HIA_per_disease_7000steps.xlsx
@@ -1,21 +1,98 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/7000 steps/Resampling/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8862D78-67D7-4B41-9B76-1FDA654F5D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>tot_cases</t>
+  </si>
+  <si>
+    <t>tot_cases_low</t>
+  </si>
+  <si>
+    <t>tot_cases_sup</t>
+  </si>
+  <si>
+    <t>tot_daly</t>
+  </si>
+  <si>
+    <t>tot_daly_low</t>
+  </si>
+  <si>
+    <t>tot_daly_sup</t>
+  </si>
+  <si>
+    <t>tot_medic_costs</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_sup</t>
+  </si>
+  <si>
+    <t>tot_soc_costs</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_sup</t>
+  </si>
+  <si>
+    <t>mort</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>bc</t>
+  </si>
+  <si>
+    <t>cancer</t>
+  </si>
+  <si>
+    <t>diab2</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>dep</t>
+  </si>
+  <si>
+    <t>Morbidity</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +140,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +192,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +226,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +261,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,82 +437,63 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_sup</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_sup</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_sup</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_sup</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>13</v>
       </c>
       <c r="B2">
         <v>172375.622</v>
@@ -440,10 +508,10 @@
         <v>281419.36</v>
       </c>
       <c r="F2">
-        <v>205733.634</v>
+        <v>205733.63399999999</v>
       </c>
       <c r="G2">
-        <v>364571.318</v>
+        <v>364571.31800000003</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,44 +523,42 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>37429617719.121</v>
+        <v>37429617719.121002</v>
       </c>
       <c r="L2">
-        <v>27405207971.793</v>
+        <v>27405207971.792999</v>
       </c>
       <c r="M2">
-        <v>48491252181.856</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
+        <v>48491252181.856003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
       </c>
       <c r="B3">
-        <v>61733.314</v>
+        <v>61733.313999999998</v>
       </c>
       <c r="C3">
         <v>37433.303</v>
       </c>
       <c r="D3">
-        <v>88204.90399999999</v>
+        <v>88204.903999999995</v>
       </c>
       <c r="E3">
         <v>9552.76</v>
       </c>
       <c r="F3">
-        <v>5782.386</v>
+        <v>5782.3860000000004</v>
       </c>
       <c r="G3">
-        <v>13659.068</v>
+        <v>13659.067999999999</v>
       </c>
       <c r="H3">
-        <v>3440382243.517</v>
+        <v>3440382243.5170002</v>
       </c>
       <c r="I3">
-        <v>2083285049.353</v>
+        <v>2083285049.3529999</v>
       </c>
       <c r="J3">
         <v>4918917378.5</v>
@@ -501,20 +567,18 @@
         <v>1271133647.421</v>
       </c>
       <c r="L3">
-        <v>771535429.337</v>
+        <v>771535429.33700001</v>
       </c>
       <c r="M3">
-        <v>1817000302.117</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>bc</t>
-        </is>
+        <v>1817000302.1170001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>15</v>
       </c>
       <c r="B4">
-        <v>4901.919</v>
+        <v>4901.9189999999999</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -523,38 +587,36 @@
         <v>10150.134</v>
       </c>
       <c r="E4">
-        <v>1357.315</v>
+        <v>1357.3150000000001</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>2817.999</v>
+        <v>2817.9989999999998</v>
       </c>
       <c r="H4">
-        <v>216189306.525</v>
+        <v>216189306.52500001</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>448597467.593</v>
+        <v>448597467.59299999</v>
       </c>
       <c r="K4">
-        <v>180545129.916</v>
+        <v>180545129.91600001</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>374563020.504</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
+        <v>374563020.50400001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>16</v>
       </c>
       <c r="B5">
         <v>32125.787</v>
@@ -563,28 +625,28 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>66662.76300000001</v>
+        <v>66662.763000000006</v>
       </c>
       <c r="E5">
-        <v>5482.507</v>
+        <v>5482.5069999999996</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>11389.815</v>
+        <v>11389.815000000001</v>
       </c>
       <c r="H5">
-        <v>475635616.627</v>
+        <v>475635616.62699997</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>986842961.6900001</v>
+        <v>986842961.69000006</v>
       </c>
       <c r="K5">
-        <v>728409642.6339999</v>
+        <v>728409642.63399994</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -593,115 +655,109 @@
         <v>1511755829.214</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>17</v>
       </c>
       <c r="B6">
-        <v>42981.465</v>
+        <v>42981.464999999997</v>
       </c>
       <c r="C6">
-        <v>2171.566</v>
+        <v>2171.5659999999998</v>
       </c>
       <c r="D6">
-        <v>81705.671</v>
+        <v>81705.671000000002</v>
       </c>
       <c r="E6">
-        <v>10537.799</v>
+        <v>10537.799000000001</v>
       </c>
       <c r="F6">
-        <v>518.302</v>
+        <v>518.30200000000002</v>
       </c>
       <c r="G6">
-        <v>20032.237</v>
+        <v>20032.237000000001</v>
       </c>
       <c r="H6">
-        <v>3228039584.576</v>
+        <v>3228039584.5760002</v>
       </c>
       <c r="I6">
-        <v>160948101.784</v>
+        <v>160948101.78400001</v>
       </c>
       <c r="J6">
-        <v>6142389971.731</v>
+        <v>6142389971.7309999</v>
       </c>
       <c r="K6">
-        <v>1400988910.205</v>
+        <v>1400988910.2049999</v>
       </c>
       <c r="L6">
-        <v>69500187.405</v>
+        <v>69500187.405000001</v>
       </c>
       <c r="M6">
-        <v>2669323078.403</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
+        <v>2669323078.4029999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
       </c>
       <c r="B7">
-        <v>20015.437</v>
+        <v>20015.437000000002</v>
       </c>
       <c r="C7">
         <v>13560.107</v>
       </c>
       <c r="D7">
-        <v>27351.407</v>
+        <v>27351.406999999999</v>
       </c>
       <c r="E7">
-        <v>4276.448</v>
+        <v>4276.4480000000003</v>
       </c>
       <c r="F7">
-        <v>2912.609</v>
+        <v>2912.6089999999999</v>
       </c>
       <c r="G7">
         <v>5818.86</v>
       </c>
       <c r="H7">
-        <v>336936413.71</v>
+        <v>336936413.70999998</v>
       </c>
       <c r="I7">
         <v>228267917.692</v>
       </c>
       <c r="J7">
-        <v>460611975.77</v>
+        <v>460611975.76999998</v>
       </c>
       <c r="K7">
-        <v>568599158.069</v>
+        <v>568599158.06900001</v>
       </c>
       <c r="L7">
-        <v>388001583.682</v>
+        <v>388001583.68199998</v>
       </c>
       <c r="M7">
-        <v>773103489.034</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
+        <v>773103489.03400004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
       </c>
       <c r="B8">
         <v>1207225.112</v>
       </c>
       <c r="C8">
-        <v>825672.841</v>
+        <v>825672.84100000001</v>
       </c>
       <c r="D8">
-        <v>1645028.046</v>
+        <v>1645028.0460000001</v>
       </c>
       <c r="E8">
-        <v>1387587.021</v>
+        <v>1387587.0209999999</v>
       </c>
       <c r="F8">
-        <v>946219.238</v>
+        <v>946219.23800000001</v>
       </c>
       <c r="G8">
-        <v>1899449.451</v>
+        <v>1899449.4509999999</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -713,7 +769,7 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>184595742003.551</v>
+        <v>184595742003.55099</v>
       </c>
       <c r="L8">
         <v>125886456946.129</v>
@@ -722,17 +778,15 @@
         <v>252469363580.521</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Morbidity</t>
-        </is>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>20</v>
       </c>
       <c r="B9">
         <v>1368983.034</v>
       </c>
       <c r="C9">
-        <v>878837.817</v>
+        <v>878837.81700000004</v>
       </c>
       <c r="D9">
         <v>1919102.925</v>
@@ -741,13 +795,13 @@
         <v>1418793.85</v>
       </c>
       <c r="F9">
-        <v>955432.535</v>
+        <v>955432.53500000003</v>
       </c>
       <c r="G9">
         <v>1953167.43</v>
       </c>
       <c r="H9">
-        <v>7697183164.955001</v>
+        <v>7697183164.9550009</v>
       </c>
       <c r="I9">
         <v>2472501068.829</v>
@@ -756,20 +810,18 @@
         <v>12957359755.284</v>
       </c>
       <c r="K9">
-        <v>188745418491.796</v>
+        <v>188745418491.79599</v>
       </c>
       <c r="L9">
-        <v>127115494146.553</v>
+        <v>127115494146.55299</v>
       </c>
       <c r="M9">
         <v>259615109299.793</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>21</v>
       </c>
       <c r="B10">
         <v>1541358.656</v>
@@ -778,7 +830,7 @@
         <v>1004484.231</v>
       </c>
       <c r="D10">
-        <v>2142760.262</v>
+        <v>2142760.2620000001</v>
       </c>
       <c r="E10">
         <v>1700213.21</v>
@@ -787,10 +839,10 @@
         <v>1161166.169</v>
       </c>
       <c r="G10">
-        <v>2317738.748</v>
+        <v>2317738.7480000001</v>
       </c>
       <c r="H10">
-        <v>7697183164.955001</v>
+        <v>7697183164.9550009</v>
       </c>
       <c r="I10">
         <v>2472501068.829</v>
@@ -799,13 +851,13 @@
         <v>12957359755.284</v>
       </c>
       <c r="K10">
-        <v>226175036210.917</v>
+        <v>226175036210.91699</v>
       </c>
       <c r="L10">
-        <v>154520702118.346</v>
+        <v>154520702118.34601</v>
       </c>
       <c r="M10">
-        <v>308106361481.649</v>
+        <v>308106361481.64899</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/7000 steps/Resampling/HIA_per_disease_7000steps.xlsx
+++ b/output/Tables/7000 steps/Resampling/HIA_per_disease_7000steps.xlsx
@@ -1,98 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/7000 steps/Resampling/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8862D78-67D7-4B41-9B76-1FDA654F5D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t>disease</t>
-  </si>
-  <si>
-    <t>tot_cases</t>
-  </si>
-  <si>
-    <t>tot_cases_low</t>
-  </si>
-  <si>
-    <t>tot_cases_sup</t>
-  </si>
-  <si>
-    <t>tot_daly</t>
-  </si>
-  <si>
-    <t>tot_daly_low</t>
-  </si>
-  <si>
-    <t>tot_daly_sup</t>
-  </si>
-  <si>
-    <t>tot_medic_costs</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_low</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_sup</t>
-  </si>
-  <si>
-    <t>tot_soc_costs</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_low</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_sup</t>
-  </si>
-  <si>
-    <t>mort</t>
-  </si>
-  <si>
-    <t>cvd</t>
-  </si>
-  <si>
-    <t>bc</t>
-  </si>
-  <si>
-    <t>cancer</t>
-  </si>
-  <si>
-    <t>diab2</t>
-  </si>
-  <si>
-    <t>dem</t>
-  </si>
-  <si>
-    <t>dep</t>
-  </si>
-  <si>
-    <t>Morbidity</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -192,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -226,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -261,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -437,81 +350,100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>13</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_low</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_sup</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_sup</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_sup</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_sup</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
       </c>
       <c r="B2">
-        <v>172375.622</v>
+        <v>159343.47</v>
       </c>
       <c r="C2">
-        <v>125646.414</v>
+        <v>136328.046</v>
       </c>
       <c r="D2">
-        <v>223657.337</v>
+        <v>180646.745</v>
       </c>
       <c r="E2">
-        <v>281419.36</v>
+        <v>1657558.21</v>
       </c>
       <c r="F2">
-        <v>205733.63399999999</v>
+        <v>1420300.69</v>
       </c>
       <c r="G2">
-        <v>364571.31800000003</v>
+        <v>1869800.909</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -523,341 +455,314 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>37429617719.121002</v>
+        <v>220475329053.966</v>
       </c>
       <c r="L2">
-        <v>27405207971.792999</v>
+        <v>188946181834.213</v>
       </c>
       <c r="M2">
-        <v>48491252181.856003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>14</v>
+        <v>248629077150.609</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
       </c>
       <c r="B3">
-        <v>61733.313999999998</v>
+        <v>144361.345</v>
       </c>
       <c r="C3">
-        <v>37433.303</v>
+        <v>92936.56200000001</v>
       </c>
       <c r="D3">
-        <v>88204.903999999995</v>
+        <v>186185.085</v>
       </c>
       <c r="E3">
-        <v>9552.76</v>
+        <v>125963.405</v>
       </c>
       <c r="F3">
-        <v>5782.3860000000004</v>
+        <v>81146.239</v>
       </c>
       <c r="G3">
-        <v>13659.067999999999</v>
+        <v>162390.865</v>
       </c>
       <c r="H3">
-        <v>3440382243.5170002</v>
+        <v>8042337974.838</v>
       </c>
       <c r="I3">
-        <v>2083285049.3529999</v>
+        <v>5176971270.234</v>
       </c>
       <c r="J3">
-        <v>4918917378.5</v>
+        <v>10369806498.873</v>
       </c>
       <c r="K3">
-        <v>1271133647.421</v>
+        <v>16755687592.818</v>
       </c>
       <c r="L3">
-        <v>771535429.33700001</v>
+        <v>10786056020.8</v>
       </c>
       <c r="M3">
-        <v>1817000302.1170001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>15</v>
+        <v>21594420280.414</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
       </c>
       <c r="B4">
-        <v>4901.9189999999999</v>
+        <v>128927.529</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>10150.134</v>
+        <v>249606.177</v>
       </c>
       <c r="E4">
-        <v>1357.3150000000001</v>
+        <v>190522.883</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>2817.9989999999998</v>
+        <v>368960.202</v>
       </c>
       <c r="H4">
-        <v>216189306.52500001</v>
+        <v>1908506994.288</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>448597467.59299999</v>
+        <v>3697150159.913</v>
       </c>
       <c r="K4">
-        <v>180545129.91600001</v>
+        <v>25341442264.667</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>374563020.50400001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>16</v>
+        <v>49078426887.372</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
       </c>
       <c r="B5">
-        <v>32125.787</v>
+        <v>28736.678</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1624.931</v>
       </c>
       <c r="D5">
-        <v>66662.763000000006</v>
+        <v>50986.199</v>
       </c>
       <c r="E5">
-        <v>5482.5069999999996</v>
+        <v>56410.932</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>3210.814</v>
       </c>
       <c r="G5">
-        <v>11389.815000000001</v>
+        <v>100150.73</v>
       </c>
       <c r="H5">
-        <v>475635616.62699997</v>
+        <v>2161593935.784</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>122451320.158</v>
       </c>
       <c r="J5">
-        <v>986842961.69000006</v>
+        <v>3833833717.977</v>
       </c>
       <c r="K5">
-        <v>728409642.63399994</v>
+        <v>7504179154.497</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>428013680.877</v>
       </c>
       <c r="M5">
-        <v>1511755829.214</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>17</v>
+        <v>13321159708.377</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
       </c>
       <c r="B6">
-        <v>42981.464999999997</v>
+        <v>49487.998</v>
       </c>
       <c r="C6">
-        <v>2171.5659999999998</v>
+        <v>37225.36</v>
       </c>
       <c r="D6">
-        <v>81705.671000000002</v>
+        <v>60374.778</v>
       </c>
       <c r="E6">
-        <v>10537.799000000001</v>
+        <v>72863.276</v>
       </c>
       <c r="F6">
-        <v>518.30200000000002</v>
+        <v>54893.59</v>
       </c>
       <c r="G6">
-        <v>20032.237000000001</v>
+        <v>88651.997</v>
       </c>
       <c r="H6">
-        <v>3228039584.5760002</v>
+        <v>833059670.77</v>
       </c>
       <c r="I6">
-        <v>160948101.78400001</v>
+        <v>626755762.442</v>
       </c>
       <c r="J6">
-        <v>6142389971.7309999</v>
+        <v>1016564619.077</v>
       </c>
       <c r="K6">
-        <v>1400988910.2049999</v>
+        <v>9688954988.832001</v>
       </c>
       <c r="L6">
-        <v>69500187.405000001</v>
+        <v>7299708900.697</v>
       </c>
       <c r="M6">
-        <v>2669323078.4029999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>18</v>
+        <v>11800493212.828</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
       </c>
       <c r="B7">
-        <v>20015.437000000002</v>
+        <v>616141.301</v>
       </c>
       <c r="C7">
-        <v>13560.107</v>
+        <v>470493.064</v>
       </c>
       <c r="D7">
-        <v>27351.406999999999</v>
+        <v>752980.325</v>
       </c>
       <c r="E7">
-        <v>4276.4480000000003</v>
+        <v>1785314.838</v>
       </c>
       <c r="F7">
-        <v>2912.6089999999999</v>
+        <v>1364330.794</v>
       </c>
       <c r="G7">
-        <v>5818.86</v>
+        <v>2181657.576</v>
       </c>
       <c r="H7">
-        <v>336936413.70999998</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>228267917.692</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>460611975.76999998</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>568599158.06900001</v>
+        <v>237482310419.563</v>
       </c>
       <c r="L7">
-        <v>388001583.68199998</v>
+        <v>181392425256.157</v>
       </c>
       <c r="M7">
-        <v>773103489.03400004</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>19</v>
+        <v>290105641002.348</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Morbidity</t>
+        </is>
       </c>
       <c r="B8">
-        <v>1207225.112</v>
+        <v>967654.851</v>
       </c>
       <c r="C8">
-        <v>825672.84100000001</v>
+        <v>602279.917</v>
       </c>
       <c r="D8">
-        <v>1645028.0460000001</v>
+        <v>1300132.564</v>
       </c>
       <c r="E8">
-        <v>1387587.0209999999</v>
+        <v>2231075.334</v>
       </c>
       <c r="F8">
-        <v>946219.23800000001</v>
+        <v>1503581.437</v>
       </c>
       <c r="G8">
-        <v>1899449.4509999999</v>
+        <v>2901811.37</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>12945498575.68</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>5926178352.834001</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>18917354995.84</v>
       </c>
       <c r="K8">
-        <v>184595742003.55099</v>
+        <v>296772574420.377</v>
       </c>
       <c r="L8">
-        <v>125886456946.129</v>
+        <v>199906203858.531</v>
       </c>
       <c r="M8">
-        <v>252469363580.521</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>20</v>
+        <v>385900141091.3391</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="B9">
-        <v>1368983.034</v>
+        <v>1126998.321</v>
       </c>
       <c r="C9">
-        <v>878837.81700000004</v>
+        <v>738607.963</v>
       </c>
       <c r="D9">
-        <v>1919102.925</v>
+        <v>1480779.309</v>
       </c>
       <c r="E9">
-        <v>1418793.85</v>
+        <v>3888633.544</v>
       </c>
       <c r="F9">
-        <v>955432.53500000003</v>
+        <v>2923882.127</v>
       </c>
       <c r="G9">
-        <v>1953167.43</v>
+        <v>4771612.278999999</v>
       </c>
       <c r="H9">
-        <v>7697183164.9550009</v>
+        <v>12945498575.68</v>
       </c>
       <c r="I9">
-        <v>2472501068.829</v>
+        <v>5926178352.834001</v>
       </c>
       <c r="J9">
-        <v>12957359755.284</v>
+        <v>18917354995.84</v>
       </c>
       <c r="K9">
-        <v>188745418491.79599</v>
+        <v>517247903474.343</v>
       </c>
       <c r="L9">
-        <v>127115494146.55299</v>
+        <v>388852385692.744</v>
       </c>
       <c r="M9">
-        <v>259615109299.793</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10">
-        <v>1541358.656</v>
-      </c>
-      <c r="C10">
-        <v>1004484.231</v>
-      </c>
-      <c r="D10">
-        <v>2142760.2620000001</v>
-      </c>
-      <c r="E10">
-        <v>1700213.21</v>
-      </c>
-      <c r="F10">
-        <v>1161166.169</v>
-      </c>
-      <c r="G10">
-        <v>2317738.7480000001</v>
-      </c>
-      <c r="H10">
-        <v>7697183164.9550009</v>
-      </c>
-      <c r="I10">
-        <v>2472501068.829</v>
-      </c>
-      <c r="J10">
-        <v>12957359755.284</v>
-      </c>
-      <c r="K10">
-        <v>226175036210.91699</v>
-      </c>
-      <c r="L10">
-        <v>154520702118.34601</v>
-      </c>
-      <c r="M10">
-        <v>308106361481.64899</v>
+        <v>634529218241.948</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/7000 steps/Resampling/HIA_per_disease_7000steps.xlsx
+++ b/output/Tables/7000 steps/Resampling/HIA_per_disease_7000steps.xlsx
@@ -372,7 +372,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>tot_cases_sup</t>
+          <t>tot_cases_up</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -387,7 +387,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>tot_daly_sup</t>
+          <t>tot_daly_up</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -402,7 +402,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>tot_medic_costs_sup</t>
+          <t>tot_medic_costs_up</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -417,7 +417,7 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>tot_soc_costs_sup</t>
+          <t>tot_soc_costs_up</t>
         </is>
       </c>
     </row>
